--- a/output/full_scan/batch_seq7_2026-09-07.xlsx
+++ b/output/full_scan/batch_seq7_2026-09-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6829</v>
+        <v>6805</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>711.8499369819847</v>
+        <v>725.67285953896</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>258</v>
+        <v>2265</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.91822795226676</v>
+        <v>64.45099247708066</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.88385902475233</v>
+        <v>29.92285642757357</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.396963245399043</v>
+        <v>0.2713825597314819</v>
       </c>
       <c r="K11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.210752027447414</v>
+        <v>14.60534777463741</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6770</v>
+        <v>6829</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>677.2235779504746</v>
+        <v>711.8499369819847</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>258</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.19645966543218</v>
+        <v>63.91822795226676</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10.60616245888797</v>
+        <v>20.88385902475233</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.204872626708969</v>
+        <v>1.396963245399043</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0095894314965763</v>
+        <v>2.210752027447414</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6668</v>
+        <v>6770</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>673.5964853162986</v>
+        <v>677.2235779504746</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>40.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.77851729050405</v>
+        <v>56.19645966543218</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>34.26285702501568</v>
+        <v>10.60616245888797</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6646757463435887</v>
+        <v>1.204872626708969</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.3736572371717266</v>
+        <v>0.0095894314965763</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6505</v>
+        <v>6668</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>668.1982545559474</v>
+        <v>673.5964853162986</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>79.7</v>
+        <v>40.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.89512266777417</v>
+        <v>55.77851729050405</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31.34798504996243</v>
+        <v>34.26285702501568</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9772597053746508</v>
+        <v>0.6646757463435887</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.6640277656309843</v>
+        <v>0.3736572371717266</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6674</v>
+        <v>6505</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>667.2193916067473</v>
+        <v>668.1982545559474</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.5</v>
+        <v>79.7</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.56643008864476</v>
+        <v>61.89512266777417</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.60540488335623</v>
+        <v>31.34798504996243</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.521939160674728</v>
+        <v>0.9772597053746508</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07103171069437859</v>
+        <v>0.6640277656309843</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6727</v>
+        <v>6674</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>665.8584900978435</v>
+        <v>667.2193916067473</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>537</v>
+        <v>16.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.83714984419432</v>
+        <v>59.56643008864476</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.09390887963304</v>
+        <v>22.60540488335623</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7532054384577199</v>
+        <v>4.521939160674728</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>6.392212218446147</v>
+        <v>0.07103171069437859</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6533</v>
+        <v>6727</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>650.4697556984021</v>
+        <v>665.8584900978435</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>257</v>
+        <v>537</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.24406869601575</v>
+        <v>61.83714984419432</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.67280885472644</v>
+        <v>31.09390887963304</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9441855043109526</v>
+        <v>0.7532054384577199</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.8803159136705361</v>
+        <v>6.392212218446147</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6830</v>
+        <v>6533</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>615.9418321060731</v>
+        <v>650.4697556984021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>582</v>
+        <v>257</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.54781015359347</v>
+        <v>56.24406869601575</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.92876441528089</v>
+        <v>20.67280885472644</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.570759525037679</v>
+        <v>0.9441855043109526</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>12.89794760501479</v>
+        <v>-0.8803159136705361</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6530</v>
+        <v>6830</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>606.0810285691807</v>
+        <v>615.9418321060731</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>94</v>
+        <v>582</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.78537649715146</v>
+        <v>67.54781015359347</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.42838785154732</v>
+        <v>33.92876441528089</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7081028569180701</v>
+        <v>0.570759525037679</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.244802019737355</v>
+        <v>12.89794760501479</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6716</v>
+        <v>6530</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>605.8298450794256</v>
+        <v>606.0810285691807</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.42591117401049</v>
+        <v>57.78537649715146</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.41383919089848</v>
+        <v>22.42838785154732</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.013180778526023</v>
+        <v>0.7081028569180701</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.17385846391865</v>
+        <v>1.244802019737355</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6584</v>
+        <v>6716</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>605.7969862892386</v>
+        <v>605.8298450794256</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>619</v>
+        <v>118</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.00749020186745</v>
+        <v>51.42591117401049</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.41015407218165</v>
+        <v>30.41383919089848</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4097573610611216</v>
+        <v>1.013180778526023</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.761148458600115</v>
+        <v>-2.17385846391865</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6531</v>
+        <v>6584</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>601.752119867078</v>
+        <v>605.7969862892386</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>960</v>
+        <v>619</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.40797017646504</v>
+        <v>53.00749020186745</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10.79025542600249</v>
+        <v>25.41015407218165</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8728557123708914</v>
+        <v>0.4097573610611216</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>6.191148642817392</v>
+        <v>2.761148458600115</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6651</v>
+        <v>6531</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>601.5640391495593</v>
+        <v>601.752119867078</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>147</v>
+        <v>960</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.05256031371441</v>
+        <v>57.40797017646504</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>28.95801788033469</v>
+        <v>10.79025542600249</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6959260247582104</v>
+        <v>0.8728557123708914</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2956268195187093</v>
+        <v>6.191148642817392</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6693</v>
+        <v>6651</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>597.4168071096839</v>
+        <v>601.5640391495593</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>184.5</v>
+        <v>147</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.53366024562595</v>
+        <v>55.05256031371441</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16.29190483698977</v>
+        <v>28.95801788033469</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.065784598958095</v>
+        <v>0.6959260247582104</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.247863152816215</v>
+        <v>0.2956268195187093</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6782</v>
+        <v>6693</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>583.1919876578825</v>
+        <v>597.4168071096839</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>229</v>
+        <v>184.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.8721440560028</v>
+        <v>54.53366024562595</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>28.66307942686312</v>
+        <v>16.29190483698977</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4904806136813128</v>
+        <v>2.065784598958095</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.063094346034342</v>
+        <v>2.247863152816215</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6739</v>
+        <v>6782</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>551.3846632127129</v>
+        <v>583.1919876578825</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1110</v>
+        <v>229</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.2173677403544</v>
+        <v>55.8721440560028</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13.65017972653158</v>
+        <v>28.66307942686312</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.650694300951803</v>
+        <v>0.4904806136813128</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>13.27656712064238</v>
+        <v>-0.063094346034342</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6655</v>
+        <v>6739</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>549.1847781288639</v>
+        <v>551.3846632127129</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>120</v>
+        <v>1110</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.44853454439736</v>
+        <v>54.2173677403544</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.06758377717111</v>
+        <v>13.65017972653158</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.518477812886386</v>
+        <v>2.650694300951803</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.594686827087025</v>
+        <v>13.27656712064238</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6741</v>
+        <v>6655</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>540.9218728989746</v>
+        <v>549.1847781288639</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>59.9</v>
+        <v>120</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>60.52493679419513</v>
+        <v>52.44853454439736</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.86858306685497</v>
+        <v>16.06758377717111</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.382760578301926</v>
+        <v>4.518477812886386</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4128495787287223</v>
+        <v>-1.594686827087025</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6548</v>
+        <v>6741</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>538.3310863584128</v>
+        <v>540.9218728989746</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.24034434283118</v>
+        <v>60.52493679419513</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12.57974428134942</v>
+        <v>30.86858306685497</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.077071209544832</v>
+        <v>0.382760578301926</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3436873675947067</v>
+        <v>0.4128495787287223</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6491</v>
+        <v>6548</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>536.6481052317421</v>
+        <v>538.3310863584128</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>379.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.93725776534607</v>
+        <v>51.24034434283118</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.08125450353271</v>
+        <v>12.57974428134942</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4854065337875044</v>
+        <v>2.077071209544832</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.4891173986698955</v>
+        <v>0.3436873675947067</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6792</v>
+        <v>6491</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>533.8991198459734</v>
+        <v>536.6481052317421</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>60.2</v>
+        <v>379.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.53748221294935</v>
+        <v>53.93725776534607</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.84668620116116</v>
+        <v>28.08125450353271</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.532888014389826</v>
+        <v>0.4854065337875044</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1418449102665735</v>
+        <v>-0.4891173986698955</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6834</v>
+        <v>6792</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>529.9061147631185</v>
+        <v>533.8991198459734</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>97</v>
+        <v>60.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>53.38426743605626</v>
+        <v>57.53748221294935</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10.05531746600098</v>
+        <v>14.84668620116116</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.347683285380348</v>
+        <v>1.532888014389826</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,48 +2160,48 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3596665519834108</v>
+        <v>0.1418449102665735</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6806</v>
+        <v>6834</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>529.9061147631185</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>3.51</v>
+        <v>97</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>31.6950221152637</v>
+        <v>53.38426743605626</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.59323562498059</v>
+        <v>10.05531746600098</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.347683285380348</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,48 +2213,48 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.4112822342230751</v>
+        <v>0.3596665519834108</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6669</v>
+        <v>6806</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>522.1770974983817</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2490</v>
+        <v>3.51</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>26.57588176580314</v>
+        <v>31.6950221152637</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>36.47417734010349</v>
+        <v>32.59323562498059</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.117709749838174</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-549.1553775419111</v>
+        <v>0.4112822342230751</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6743</v>
+        <v>6669</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>519.2455207076258</v>
+        <v>522.1770974983817</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>28.65</v>
+        <v>2490</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>58.96796633118621</v>
+        <v>26.57588176580314</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.95603430960196</v>
+        <v>36.47417734010349</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.968427857374576</v>
+        <v>2.117709749838174</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4275519969067176</v>
+        <v>-549.1553775419111</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6654</v>
+        <v>6743</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>516.8057552347682</v>
+        <v>519.2455207076258</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>215</v>
+        <v>28.65</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>67.61181966102345</v>
+        <v>58.96796633118621</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.53141000563678</v>
+        <v>21.95603430960196</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.415716916504609</v>
+        <v>0.968427857374576</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>5.618532408880654</v>
+        <v>0.4275519969067176</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6689</v>
+        <v>6654</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>511.3123652531</v>
+        <v>516.8057552347682</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>62</v>
+        <v>215</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.22268993235825</v>
+        <v>67.61181966102345</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12.48286710444176</v>
+        <v>25.53141000563678</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8087897824930625</v>
+        <v>1.415716916504609</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0274266432375002</v>
+        <v>5.618532408880654</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6613</v>
+        <v>6689</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>496.7491240098194</v>
+        <v>511.3123652531</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>265</v>
+        <v>62</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.32151734438713</v>
+        <v>51.22268993235825</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.54531241692722</v>
+        <v>12.48286710444176</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.612119933822217</v>
+        <v>0.8087897824930625</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>2.288665553622181</v>
+        <v>0.0274266432375002</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6811</v>
+        <v>6613</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>481.6262996537022</v>
+        <v>496.7491240098194</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>223.5</v>
+        <v>265</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.19391695336008</v>
+        <v>46.32151734438713</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10.31708738381623</v>
+        <v>10.54531241692722</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.87939854796686</v>
+        <v>0.612119933822217</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.5688737707966049</v>
+        <v>2.288665553622181</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6526</v>
+        <v>6811</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>477.0821805255479</v>
+        <v>481.6262996537022</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>644</v>
+        <v>223.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.60869265749621</v>
+        <v>47.19391695336008</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.78109528751872</v>
+        <v>10.31708738381623</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.534058637073183</v>
+        <v>5.87939854796686</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>5.980076634174292</v>
+        <v>-0.5688737707966049</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6664</v>
+        <v>6526</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>471.5137790652774</v>
+        <v>477.0821805255479</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>356.5</v>
+        <v>644</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,49 +2619,49 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.88775441458194</v>
+        <v>57.60869265749621</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13.41364823823316</v>
+        <v>16.78109528751872</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6703953023943597</v>
+        <v>1.534058637073183</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.811097299573315</v>
+        <v>5.980076634174292</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6683</v>
+        <v>6664</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>470.8903312850787</v>
+        <v>471.5137790652774</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1410</v>
+        <v>356.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.25622590098405</v>
+        <v>50.88775441458194</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.18395143050002</v>
+        <v>13.41364823823316</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.801129631315716</v>
+        <v>0.6703953023943597</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>33.72718392496021</v>
+        <v>1.811097299573315</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6504</v>
+        <v>6683</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>440.0816831365584</v>
+        <v>470.8903312850787</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>37.7</v>
+        <v>1410</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>48.91092129889756</v>
+        <v>58.25622590098405</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12.27173429108471</v>
+        <v>16.18395143050002</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.44461498651221</v>
+        <v>1.801129631315716</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0737444304993336</v>
+        <v>33.72718392496021</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6753</v>
+        <v>6504</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>433.3159450813674</v>
+        <v>440.0816831365584</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>137.5</v>
+        <v>37.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>46.61868447912755</v>
+        <v>48.91092129889756</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.70926262696689</v>
+        <v>12.27173429108471</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.2129401307242771</v>
+        <v>3.44461498651221</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.8004263271739631</v>
+        <v>-0.0737444304993336</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6680</v>
+        <v>6753</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>432.923404427158</v>
+        <v>433.3159450813674</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>55.3</v>
+        <v>137.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.76558651509563</v>
+        <v>46.61868447912755</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7.758486731598583</v>
+        <v>22.70926262696689</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3963022044550364</v>
+        <v>0.2129401307242771</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.349019992052765</v>
+        <v>-0.8004263271739631</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6561</v>
+        <v>6680</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>428.8793948678093</v>
+        <v>432.923404427158</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>322</v>
+        <v>55.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.03523694817903</v>
+        <v>52.76558651509563</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8.183033923123091</v>
+        <v>7.758486731598583</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.466686971555666</v>
+        <v>0.3963022044550364</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.381854328258487</v>
+        <v>1.349019992052765</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>macd_golden_cross, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6517</v>
+        <v>6561</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>425.1837805722309</v>
+        <v>428.8793948678093</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>67.3</v>
+        <v>322</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.65978069452876</v>
+        <v>47.03523694817903</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.09338131286404</v>
+        <v>8.183033923123091</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5394920535815614</v>
+        <v>1.466686971555666</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.07519455519659669</v>
+        <v>0.381854328258487</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6789</v>
+        <v>6517</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>424.4769392275857</v>
+        <v>425.1837805722309</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>471</v>
+        <v>67.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.54077753048395</v>
+        <v>49.65978069452876</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17.01085905470674</v>
+        <v>18.09338131286404</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7431613469343354</v>
+        <v>0.5394920535815614</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>5.224953980897143</v>
+        <v>0.07519455519659669</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6761</v>
+        <v>6789</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>420.2728614445448</v>
+        <v>424.4769392275857</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>180</v>
+        <v>471</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.56063852815262</v>
+        <v>54.54077753048395</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.88766405456317</v>
+        <v>17.01085905470674</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4582170523445816</v>
+        <v>0.7431613469343354</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.626204012007074</v>
+        <v>5.224953980897143</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6585</v>
+        <v>6761</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>419.1181233306006</v>
+        <v>420.2728614445448</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>46.64223369371258</v>
+        <v>51.56063852815262</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.47746381962003</v>
+        <v>19.88766405456317</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8186872844063562</v>
+        <v>0.4582170523445816</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0311435576824383</v>
+        <v>-0.626204012007074</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6515</v>
+        <v>6585</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>414.0917279702986</v>
+        <v>419.1181233306006</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>7000</v>
+        <v>114</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.34835623476342</v>
+        <v>46.64223369371258</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.91825056539976</v>
+        <v>18.47746381962003</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9755513592507308</v>
+        <v>0.8186872844063562</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>125.0869442212377</v>
+        <v>0.0311435576824383</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6657</v>
+        <v>6515</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>404.0749267985965</v>
+        <v>414.0917279702986</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>30.45</v>
+        <v>7000</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.33656233782291</v>
+        <v>56.34835623476342</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.45465569936783</v>
+        <v>15.91825056539976</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.368444604728776</v>
+        <v>0.9755513592507308</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.1852236581451198</v>
+        <v>125.0869442212377</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6771</v>
+        <v>6657</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>402.2473391933577</v>
+        <v>404.0749267985965</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>41.8</v>
+        <v>30.45</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>57.22295246701989</v>
+        <v>46.33656233782291</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>30.65729198235654</v>
+        <v>19.45465569936783</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3110945727135335</v>
+        <v>2.368444604728776</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1079867799155652</v>
+        <v>0.1852236581451198</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6692</v>
+        <v>6771</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>399.3117193241909</v>
+        <v>402.2473391933577</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>23.35</v>
+        <v>41.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.64329360366028</v>
+        <v>57.22295246701989</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8.478035322974717</v>
+        <v>30.65729198235654</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.758863432345474</v>
+        <v>0.3110945727135335</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1091328754212152</v>
+        <v>-0.1079867799155652</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6756</v>
+        <v>6692</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>397.7073678422526</v>
+        <v>399.3117193241909</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>23.35</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.20747802780924</v>
+        <v>48.64329360366028</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12.14527564090765</v>
+        <v>8.478035322974717</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8242038061499789</v>
+        <v>0.758863432345474</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0254342340105664</v>
+        <v>-0.1091328754212152</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6568</v>
+        <v>6756</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>397.4526610212648</v>
+        <v>397.7073678422526</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>135</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.40258344593851</v>
+        <v>51.20747802780924</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>31.47782245599289</v>
+        <v>12.14527564090765</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5274537207336034</v>
+        <v>0.8242038061499789</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.70012392612706</v>
+        <v>0.0254342340105664</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6796</v>
+        <v>6568</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>388.3864041747977</v>
+        <v>397.4526610212648</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>58.6</v>
+        <v>135</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.36513817513215</v>
+        <v>49.40258344593851</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.27156603281686</v>
+        <v>31.47782245599289</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.621969477206546</v>
+        <v>0.5274537207336034</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.4070709667147156</v>
+        <v>1.70012392612706</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6788</v>
+        <v>6796</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>384.1821979472226</v>
+        <v>388.3864041747977</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>358.5</v>
+        <v>58.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.08354935318417</v>
+        <v>44.36513817513215</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.34154066989818</v>
+        <v>25.27156603281686</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.241271283505938</v>
+        <v>2.621969477206546</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.8587130889521304</v>
+        <v>-0.4070709667147156</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6581</v>
+        <v>6788</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>383.4189784379787</v>
+        <v>384.1821979472226</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>109</v>
+        <v>358.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.8124315499245</v>
+        <v>49.08354935318417</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.98568936107586</v>
+        <v>16.34154066989818</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7739367583106066</v>
+        <v>1.241271283505938</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0618168057920024</v>
+        <v>0.8587130889521304</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6486</v>
+        <v>6581</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>379.2731053457674</v>
+        <v>383.4189784379787</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>109</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>67.45341346672072</v>
+        <v>54.8124315499245</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>35.3288518724532</v>
+        <v>21.98568936107586</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.02731053457674</v>
+        <v>0.7739367583106066</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.077810531273255</v>
+        <v>0.0618168057920024</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6807</v>
+        <v>6486</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>377.1431253911053</v>
+        <v>379.2731053457674</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>33.75</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.36829813211463</v>
+        <v>67.45341346672072</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.61495076885769</v>
+        <v>35.3288518724532</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.507677927627187</v>
+        <v>1.02731053457674</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.3627042456205375</v>
+        <v>1.077810531273255</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6494</v>
+        <v>6807</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>373.4649838556349</v>
+        <v>377.1431253911053</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>55.1</v>
+        <v>33.75</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.45613925661242</v>
+        <v>42.36829813211463</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10.57460138965863</v>
+        <v>24.61495076885769</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8550786971611146</v>
+        <v>2.507677927627187</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.2007616796090139</v>
+        <v>-0.3627042456205375</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6831</v>
+        <v>6494</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>371.7753224001683</v>
+        <v>373.4649838556349</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>568</v>
+        <v>55.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.44642532101543</v>
+        <v>52.45613925661242</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.83461717967723</v>
+        <v>10.57460138965863</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.163119647654884</v>
+        <v>0.8550786971611146</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.917247648917229</v>
+        <v>0.2007616796090139</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6763</v>
+        <v>6831</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>370.0336921830203</v>
+        <v>371.7753224001683</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>40.9</v>
+        <v>568</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,49 +3838,49 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>38.06262593089775</v>
+        <v>42.44642532101543</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.82450240334538</v>
+        <v>12.83461717967723</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.277339239496571</v>
+        <v>1.163119647654884</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0331661919319288</v>
+        <v>0.917247648917229</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6679</v>
+        <v>6763</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>362.535189214678</v>
+        <v>370.0336921830203</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>207</v>
+        <v>40.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,49 +3891,49 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.38208913252459</v>
+        <v>38.06262593089775</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.70548322763779</v>
+        <v>21.82450240334538</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3.875864301340116</v>
+        <v>1.277339239496571</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>2.184591584660065</v>
+        <v>-0.0331661919319288</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6715</v>
+        <v>6679</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>361.8079425026292</v>
+        <v>362.535189214678</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>339</v>
+        <v>207</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.83684107955048</v>
+        <v>47.38208913252459</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.47846526775698</v>
+        <v>17.70548322763779</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.097786698385838</v>
+        <v>3.875864301340116</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-6.504441391431508</v>
+        <v>2.184591584660065</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6642</v>
+        <v>6715</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>359.3356071411006</v>
+        <v>361.8079425026292</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>80.5</v>
+        <v>339</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.78426267493048</v>
+        <v>44.83684107955048</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.02166054357496</v>
+        <v>13.47846526775698</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6937192761934766</v>
+        <v>1.097786698385838</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.07988442445156239</v>
+        <v>-6.504441391431508</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6722</v>
+        <v>6642</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>356.8139892636404</v>
+        <v>359.3356071411006</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>32.9</v>
+        <v>80.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.20694686569921</v>
+        <v>50.78426267493048</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>25.03223041430915</v>
+        <v>19.02166054357496</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.207857160719198</v>
+        <v>0.6937192761934766</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1193470247705345</v>
+        <v>0.07988442445156239</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6708</v>
+        <v>6722</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>341.9455387570889</v>
+        <v>356.8139892636404</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>38.5</v>
+        <v>32.9</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.81887125273852</v>
+        <v>47.20694686569921</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7.157077383178589</v>
+        <v>25.03223041430915</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.094553875708891</v>
+        <v>2.207857160719198</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0112763814096443</v>
+        <v>0.1193470247705345</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6691</v>
+        <v>6708</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>340.2870291152767</v>
+        <v>341.9455387570889</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>624</v>
+        <v>38.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.48605516516698</v>
+        <v>51.81887125273852</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.30296017016378</v>
+        <v>7.157077383178589</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7658432247250584</v>
+        <v>2.094553875708891</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.13975527396023</v>
+        <v>-0.0112763814096443</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6658</v>
+        <v>6691</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>339.836940514536</v>
+        <v>340.2870291152767</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>175.5</v>
+        <v>624</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.83757426023074</v>
+        <v>42.48605516516698</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.57758198757647</v>
+        <v>22.30296017016378</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6052790890455151</v>
+        <v>0.7658432247250584</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>2.07365869945044</v>
+        <v>-1.13975527396023</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6556</v>
+        <v>6658</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>334.4846849694126</v>
+        <v>339.836940514536</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>61.5</v>
+        <v>175.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.61133871727308</v>
+        <v>54.83757426023074</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.57568653012345</v>
+        <v>17.57758198757647</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4475747943201315</v>
+        <v>0.6052790890455151</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.4185288278463992</v>
+        <v>2.07365869945044</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6534</v>
+        <v>6556</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>332.1242547528595</v>
+        <v>334.4846849694126</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>50.6599921693342</v>
+        <v>47.61133871727308</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.77647779336402</v>
+        <v>13.57568653012345</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9326465072503912</v>
+        <v>0.4475747943201315</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0571163137547317</v>
+        <v>0.4185288278463992</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6768</v>
+        <v>6534</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>318.216361490411</v>
+        <v>332.1242547528595</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>63.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>35.57760481980341</v>
+        <v>50.6599921693342</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>28.36996575287944</v>
+        <v>11.77647779336402</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6499424657596922</v>
+        <v>0.9326465072503912</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2046626873703854</v>
+        <v>-0.0571163137547317</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6577</v>
+        <v>6768</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>317.5094113522397</v>
+        <v>318.216361490411</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>80</v>
+        <v>63.8</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,49 +4421,49 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.15469534869891</v>
+        <v>35.57760481980341</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.8252722454843</v>
+        <v>28.36996575287944</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5631154205724642</v>
+        <v>0.6499424657596922</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1100889576167383</v>
+        <v>0.2046626873703854</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6735</v>
+        <v>6577</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>315.8907597193967</v>
+        <v>317.5094113522397</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>62.8</v>
+        <v>80</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,49 +4474,49 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.40268034925621</v>
+        <v>49.15469534869891</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.43561734825382</v>
+        <v>17.8252722454843</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4364999047528336</v>
+        <v>0.5631154205724642</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5074941833167732</v>
+        <v>-0.1100889576167383</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6794</v>
+        <v>6735</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>305.8126123867743</v>
+        <v>315.8907597193967</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>75</v>
+        <v>62.8</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.2079025436334</v>
+        <v>44.40268034925621</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.79605381514198</v>
+        <v>14.43561734825382</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4474378296910324</v>
+        <v>0.4364999047528336</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1876428622038356</v>
+        <v>0.5074941833167732</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4555,21 +4555,21 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6720</v>
+        <v>6794</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>302.7085304716734</v>
+        <v>305.8126123867743</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.85125108502475</v>
+        <v>49.2079025436334</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>29.55596485889368</v>
+        <v>18.79605381514198</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5226307642054734</v>
+        <v>0.4474378296910324</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.2234422779690039</v>
+        <v>0.1876428622038356</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6598</v>
+        <v>6720</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>301.2677747236012</v>
+        <v>302.7085304716734</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>27.1</v>
+        <v>132</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.3920065403051</v>
+        <v>42.85125108502475</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.94408286834645</v>
+        <v>29.55596485889368</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3100738603881708</v>
+        <v>0.5226307642054734</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.2258454261330944</v>
+        <v>-0.2234422779690039</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6525</v>
+        <v>6598</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>299.1495819019125</v>
+        <v>301.2677747236012</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>133.5</v>
+        <v>27.1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.950667854826</v>
+        <v>44.3920065403051</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>8.933061956436813</v>
+        <v>17.94408286834645</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7033037711977962</v>
+        <v>0.3100738603881708</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2775299692666459</v>
+        <v>-0.2258454261330944</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6706</v>
+        <v>6525</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>295.5328724416419</v>
+        <v>299.1495819019125</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>123.5</v>
+        <v>133.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.08125555592324</v>
+        <v>42.950667854826</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.09339560863647</v>
+        <v>8.933061956436813</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6460566232054008</v>
+        <v>0.7033037711977962</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.9584948412740346</v>
+        <v>-0.2775299692666459</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6643</v>
+        <v>6706</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>290.2286581282301</v>
+        <v>295.5328724416419</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>411</v>
+        <v>123.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.48046727508817</v>
+        <v>52.08125555592324</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.04903149944997</v>
+        <v>17.09339560863647</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5151015698496764</v>
+        <v>0.6460566232054008</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.7389630934692484</v>
+        <v>0.9584948412740346</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6477</v>
+        <v>6643</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>289.391503923072</v>
+        <v>290.2286581282301</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>34.6</v>
+        <v>411</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.24101703195086</v>
+        <v>45.48046727508817</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.91995028962209</v>
+        <v>10.04903149944997</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.1807595590306576</v>
+        <v>0.5151015698496764</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.2718897612703115</v>
+        <v>-0.7389630934692484</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6488</v>
+        <v>6477</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>287.272950063887</v>
+        <v>289.391503923072</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>971</v>
+        <v>34.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.37789746640563</v>
+        <v>43.24101703195086</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8.657313167233223</v>
+        <v>16.91995028962209</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8528368212794664</v>
+        <v>0.1807595590306576</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>4.292287053468492</v>
+        <v>-0.2718897612703115</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6606</v>
+        <v>6488</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>286.9011571710897</v>
+        <v>287.272950063887</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>25.05</v>
+        <v>971</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>35.96959746977963</v>
+        <v>49.37789746640563</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.3681496699947</v>
+        <v>8.657313167233223</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.590115717108974</v>
+        <v>0.8528368212794664</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1290961907287599</v>
+        <v>4.292287053468492</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6690</v>
+        <v>6606</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>284.104335536873</v>
+        <v>286.9011571710897</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>163</v>
+        <v>25.05</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.7388144492567</v>
+        <v>35.96959746977963</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>9.044133045325149</v>
+        <v>11.3681496699947</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6535575365046159</v>
+        <v>1.590115717108974</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1022458405281816</v>
+        <v>-0.1290961907287599</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6573</v>
+        <v>6690</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>278.1128665062773</v>
+        <v>284.104335536873</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>16.2</v>
+        <v>163</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>42.41050970082716</v>
+        <v>46.7388144492567</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>18.88485366238547</v>
+        <v>9.044133045325149</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7045405459264217</v>
+        <v>0.6535575365046159</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0178630336871137</v>
+        <v>-0.1022458405281816</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6645</v>
+        <v>6573</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>270.7449022421657</v>
+        <v>278.1128665062773</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>12.2</v>
+        <v>16.2</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>33.99019379009235</v>
+        <v>42.41050970082716</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>30.75295983157886</v>
+        <v>18.88485366238547</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.474028145699348</v>
+        <v>0.7045405459264217</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.023337656361123</v>
+        <v>-0.0178630336871137</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6498</v>
+        <v>6645</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>269.9974325598926</v>
+        <v>270.7449022421657</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.7808376849832</v>
+        <v>33.99019379009235</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>20.39300694341512</v>
+        <v>30.75295983157886</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.81188066525729</v>
+        <v>1.474028145699348</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.3192664999560215</v>
+        <v>-0.023337656361123</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6597</v>
+        <v>6498</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>266.1856717814005</v>
+        <v>269.9974325598926</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>72.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.02495112064468</v>
+        <v>44.7808376849832</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7.448483203777862</v>
+        <v>20.39300694341512</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1200884862530285</v>
+        <v>1.81188066525729</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>2.807440161362629</v>
+        <v>0.3192664999560215</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6803</v>
+        <v>6597</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>264.9939314772639</v>
+        <v>266.1856717814005</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>271.5</v>
+        <v>72.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.60920070419319</v>
+        <v>52.02495112064468</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.71176963578912</v>
+        <v>7.448483203777862</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.391870886386762</v>
+        <v>0.1200884862530285</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.4633186370018489</v>
+        <v>2.807440161362629</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6512</v>
+        <v>6803</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>264.0735909193847</v>
+        <v>264.9939314772639</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>20.2</v>
+        <v>271.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>52.56398962784893</v>
+        <v>52.60920070419319</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>9.583681857266132</v>
+        <v>16.71176963578912</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.1914689597574932</v>
+        <v>1.391870886386762</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.4071044321760151</v>
+        <v>0.4633186370018489</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6821</v>
+        <v>6512</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>256.7893394426222</v>
+        <v>264.0735909193847</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>40.95</v>
+        <v>20.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.59986271226789</v>
+        <v>52.56398962784893</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.67101721563644</v>
+        <v>9.583681857266132</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.560118357558687</v>
+        <v>0.1914689597574932</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.3120012467502266</v>
+        <v>0.4071044321760151</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6541</v>
+        <v>6821</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>252.9523989562553</v>
+        <v>256.7893394426222</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>31.6</v>
+        <v>40.95</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>27.673031635577</v>
+        <v>42.59986271226789</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>24.30596218826572</v>
+        <v>14.67101721563644</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7480528880152824</v>
+        <v>1.560118357558687</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.4679900458463442</v>
+        <v>0.3120012467502266</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6579</v>
+        <v>6541</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>251.6639829341306</v>
+        <v>252.9523989562553</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>152</v>
+        <v>31.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.14374827024852</v>
+        <v>27.673031635577</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.26420723279898</v>
+        <v>24.30596218826572</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8149653751886423</v>
+        <v>0.7480528880152824</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.4994941492057521</v>
+        <v>-0.4679900458463442</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6742</v>
+        <v>6579</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>249.1904663372072</v>
+        <v>251.6639829341306</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>44.2</v>
+        <v>152</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.69302663604716</v>
+        <v>49.14374827024852</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>19.92217842093749</v>
+        <v>16.26420723279898</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8720911368830969</v>
+        <v>0.8149653751886423</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.4042217035760923</v>
+        <v>0.4994941492057521</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6754</v>
+        <v>6742</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>240.6161208295145</v>
+        <v>249.1904663372072</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>42.65</v>
+        <v>44.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>55.36452410598818</v>
+        <v>46.69302663604716</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.31197664652851</v>
+        <v>19.92217842093749</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.31565917185179</v>
+        <v>0.8720911368830969</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0733523978841437</v>
+        <v>0.4042217035760923</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6582</v>
+        <v>6754</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>236.9295778838265</v>
+        <v>240.6161208295145</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>31.9</v>
+        <v>42.65</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>47.00666683303904</v>
+        <v>55.36452410598818</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24.28268706921581</v>
+        <v>12.31197664652851</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6282485454373542</v>
+        <v>1.31565917185179</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0426457773562046</v>
+        <v>0.0733523978841437</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6605</v>
+        <v>6582</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>232.572113166422</v>
+        <v>236.9295778838265</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>137.5</v>
+        <v>31.9</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.50321856627117</v>
+        <v>47.00666683303904</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.12258179514857</v>
+        <v>24.28268706921581</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6279534714649219</v>
+        <v>0.6282485454373542</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.4067959357572845</v>
+        <v>-0.0426457773562046</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6719</v>
+        <v>6605</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>228.2613410998359</v>
+        <v>232.572113166422</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>190</v>
+        <v>137.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.4555349866019</v>
+        <v>49.50321856627117</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22.8796327654193</v>
+        <v>13.12258179514857</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4735774644555336</v>
+        <v>0.6279534714649219</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1.101265841367933</v>
+        <v>-0.4067959357572845</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6570</v>
+        <v>6719</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>224.5732022575708</v>
+        <v>228.2613410998359</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>50.5</v>
+        <v>190</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.32233459031901</v>
+        <v>39.4555349866019</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.37105983289673</v>
+        <v>22.8796327654193</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7635742354861891</v>
+        <v>0.4735774644555336</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.4148991419386575</v>
+        <v>1.101265841367933</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6560</v>
+        <v>6570</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>220.9899565716531</v>
+        <v>224.5732022575708</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>30.9</v>
+        <v>50.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.16703224068976</v>
+        <v>41.32233459031901</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.38995180656611</v>
+        <v>16.37105983289673</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6806948504344585</v>
+        <v>0.7635742354861891</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.5733839578586388</v>
+        <v>-0.4148991419386575</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6698</v>
+        <v>6560</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>216.8289254410899</v>
+        <v>220.9899565716531</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>31.6</v>
+        <v>30.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.85071681841463</v>
+        <v>50.16703224068976</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.67395038119611</v>
+        <v>14.38995180656611</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.958844869336646</v>
+        <v>0.6806948504344585</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1862088044623255</v>
+        <v>0.5733839578586388</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6781</v>
+        <v>6698</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>212.1538798760177</v>
+        <v>216.8289254410899</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>1080</v>
+        <v>31.6</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.21184686658896</v>
+        <v>43.85071681841463</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.05434313371575</v>
+        <v>17.67395038119611</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7072889302420525</v>
+        <v>0.958844869336646</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.90431969985422</v>
+        <v>0.1862088044623255</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6695</v>
+        <v>6781</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>211.6469273602777</v>
+        <v>212.1538798760177</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>48.6</v>
+        <v>1080</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.09603327231269</v>
+        <v>49.21184686658896</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.86057274807119</v>
+        <v>12.05434313371575</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7921776374894711</v>
+        <v>0.7072889302420525</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2920357442736514</v>
+        <v>-0.90431969985422</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6835</v>
+        <v>6695</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>206.6472696746477</v>
+        <v>211.6469273602777</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>31.3</v>
+        <v>48.6</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>49.62814699901392</v>
+        <v>46.09603327231269</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.56433532044355</v>
+        <v>12.86057274807119</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.119757365684575</v>
+        <v>0.7921776374894711</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1195300024161393</v>
+        <v>0.2920357442736514</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6614</v>
+        <v>6835</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>204.5262464626024</v>
+        <v>206.6472696746477</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>35.85</v>
+        <v>31.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.08696135246452</v>
+        <v>49.62814699901392</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.894434374127052</v>
+        <v>13.56433532044355</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8719551568021811</v>
+        <v>1.119757365684575</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0777763236011467</v>
+        <v>0.1195300024161393</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6757</v>
+        <v>6614</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>203.1862661517358</v>
+        <v>204.5262464626024</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>55.5</v>
+        <v>35.85</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.6727672376946</v>
+        <v>44.08696135246452</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>9.44060295731493</v>
+        <v>9.894434374127052</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6024805359631755</v>
+        <v>0.8719551568021811</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0257371767078844</v>
+        <v>0.0777763236011467</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6485</v>
+        <v>6757</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>201.5296768676</v>
+        <v>203.1862661517358</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>61.8</v>
+        <v>55.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.09964724467947</v>
+        <v>46.6727672376946</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.73345447293606</v>
+        <v>9.44060295731493</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5430576773526289</v>
+        <v>0.6024805359631755</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.4816073430301149</v>
+        <v>0.0257371767078844</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6558</v>
+        <v>6485</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>200.1808257312158</v>
+        <v>201.5296768676</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>24.25</v>
+        <v>61.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.15768892310828</v>
+        <v>47.09964724467947</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>26.53618397463324</v>
+        <v>15.73345447293606</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.126501303046094</v>
+        <v>0.5430576773526289</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0247259986095799</v>
+        <v>0.4816073430301149</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6823</v>
+        <v>6558</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>196.80997209776</v>
+        <v>200.1808257312158</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>60.1</v>
+        <v>24.25</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>38.89650080747733</v>
+        <v>39.15768892310828</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.90889174677825</v>
+        <v>26.53618397463324</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8313465482250155</v>
+        <v>1.126501303046094</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1249584445773677</v>
+        <v>0.0247259986095799</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6591</v>
+        <v>6823</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>195.4910153869203</v>
+        <v>196.80997209776</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>42.05</v>
+        <v>60.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>34.97539356886803</v>
+        <v>38.89650080747733</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>29.03145645282425</v>
+        <v>20.90889174677825</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.077403017454991</v>
+        <v>0.8313465482250155</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1080207361621945</v>
+        <v>-0.1249584445773677</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6671</v>
+        <v>6591</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>192.5920845512964</v>
+        <v>195.4910153869203</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>23.1</v>
+        <v>42.05</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>49.4106814306477</v>
+        <v>34.97539356886803</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.56526759325096</v>
+        <v>29.03145645282425</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2472458577488617</v>
+        <v>1.077403017454991</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0751770051090265</v>
+        <v>0.1080207361621945</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6592</v>
+        <v>6671</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>184.0713636459658</v>
+        <v>192.5920845512964</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>60.6</v>
+        <v>23.1</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>47.2041252572889</v>
+        <v>49.4106814306477</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>9.715189574802331</v>
+        <v>15.56526759325096</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.178218275024613</v>
+        <v>0.2472458577488617</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0227485309707737</v>
+        <v>0.0751770051090265</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6552</v>
+        <v>6592</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>179.5169335860723</v>
+        <v>184.0713636459658</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>24</v>
+        <v>60.6</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>37.16018727061246</v>
+        <v>47.2041252572889</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.17869025942964</v>
+        <v>9.715189574802331</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.731595901548162</v>
+        <v>1.178218275024613</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0010377586957452</v>
+        <v>-0.0227485309707737</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6790</v>
+        <v>6552</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>177.9195422452611</v>
+        <v>179.5169335860723</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>38.1</v>
+        <v>24</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>45.63276382684416</v>
+        <v>37.16018727061246</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>10.82522524965748</v>
+        <v>13.17869025942964</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4849766073089727</v>
+        <v>0.731595901548162</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0490589085150482</v>
+        <v>0.0010377586957452</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6725</v>
+        <v>6790</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>167.6951626789335</v>
+        <v>177.9195422452611</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>227.5</v>
+        <v>38.1</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>41.89753165974548</v>
+        <v>45.63276382684416</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>30.60825105214358</v>
+        <v>10.82522524965748</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7876936595650946</v>
+        <v>0.4849766073089727</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>2.203821688564469</v>
+        <v>0.0490589085150482</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6625</v>
+        <v>6725</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>166.8366966883708</v>
+        <v>167.6951626789335</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>75.8</v>
+        <v>227.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>44.61381256796987</v>
+        <v>41.89753165974548</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>9.392802717602891</v>
+        <v>30.60825105214358</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.88275537921417</v>
+        <v>0.7876936595650946</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.198745035147765</v>
+        <v>2.203821688564469</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6641</v>
+        <v>6625</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>161.2176209823146</v>
+        <v>166.8366966883708</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>17.25</v>
+        <v>75.8</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>38.76051931702429</v>
+        <v>44.61381256796987</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7.594226198781475</v>
+        <v>9.392802717602891</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4441449148303849</v>
+        <v>0.88275537921417</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0757560113854939</v>
+        <v>-0.198745035147765</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6684</v>
+        <v>6641</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>158.655022616807</v>
+        <v>161.2176209823146</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>45.85</v>
+        <v>17.25</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.15771869647809</v>
+        <v>38.76051931702429</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.0216534744918</v>
+        <v>7.594226198781475</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.8691198285068842</v>
+        <v>0.4441449148303849</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0682522676711613</v>
+        <v>-0.0757560113854939</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6799</v>
+        <v>6684</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>156.3416163897511</v>
+        <v>158.655022616807</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>45.85</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.32015441572982</v>
+        <v>42.15771869647809</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.76706540434664</v>
+        <v>11.0216534744918</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6641383278624987</v>
+        <v>0.8691198285068842</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.2544917961451909</v>
+        <v>0.0682522676711613</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6546</v>
+        <v>6799</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>155.5046095650279</v>
+        <v>156.3416163897511</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>61.9</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>47.01908528180562</v>
+        <v>43.32015441572982</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.47218711917417</v>
+        <v>11.76706540434664</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.8827220193205149</v>
+        <v>0.6641383278624987</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.009577189654004101</v>
+        <v>0.2544917961451909</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6589</v>
+        <v>6546</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>152.5217898844684</v>
+        <v>155.5046095650279</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>47.5</v>
+        <v>61.9</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.90978064183059</v>
+        <v>47.01908528180562</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>19.11020796383597</v>
+        <v>14.47218711917417</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.6243761152594233</v>
+        <v>0.8827220193205149</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.4058736943072513</v>
+        <v>-0.009577189654004101</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6776</v>
+        <v>6589</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>103.72591617863</v>
+        <v>152.5217898844684</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>53</v>
+        <v>47.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.02200093499564</v>
+        <v>43.90978064183059</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.60174466435106</v>
+        <v>19.11020796383597</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.236912706624722</v>
+        <v>0.6243761152594233</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0154272637468155</v>
+        <v>-0.4058736943072513</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6550</v>
+        <v>6776</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>103.0028062836154</v>
+        <v>103.72591617863</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>10.3</v>
+        <v>53</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>39.22755748482543</v>
+        <v>43.02200093499564</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>19.49501683409859</v>
+        <v>15.60174466435106</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.529843166556389</v>
+        <v>1.236912706624722</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0374584498477847</v>
+        <v>0.0154272637468155</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6732</v>
+        <v>6550</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>93.95459683540804</v>
+        <v>103.0028062836154</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>148.5</v>
+        <v>10.3</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>38.11312276774946</v>
+        <v>39.22755748482543</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.11582489785187</v>
+        <v>19.49501683409859</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4598559569423083</v>
+        <v>0.529843166556389</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.4927209192932684</v>
+        <v>-0.0374584498477847</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,52 +7152,105 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6732</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>昇佳電子</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>93.95459683540804</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>38.11312276774946</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>18.11582489785187</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.4598559569423083</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.4927209192932684</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6624</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>萬年清</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>44.90892477831401</v>
       </c>
-      <c r="E127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="E128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>37.19851090411846</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>8.040710558890101</v>
       </c>
-      <c r="J127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="J128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>-2.61020671256283</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
